--- a/docs/quality/golden-reports/income-expense-xlsx.xlsx
+++ b/docs/quality/golden-reports/income-expense-xlsx.xlsx
@@ -507,7 +507,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Prepared by admin · Generated 14 Aug 2026 10:35</t>
+          <t>Prepared by admin · Generated 14 Aug 2026 16:41</t>
         </is>
       </c>
     </row>
